--- a/artfynd/A 59742-2024 artfynd.xlsx
+++ b/artfynd/A 59742-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127013878</v>
       </c>
       <c r="B2" t="n">
-        <v>88654</v>
+        <v>88722</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59742-2024 artfynd.xlsx
+++ b/artfynd/A 59742-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127013878</v>
       </c>
       <c r="B2" t="n">
-        <v>88722</v>
+        <v>88728</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59742-2024 artfynd.xlsx
+++ b/artfynd/A 59742-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127013878</v>
       </c>
       <c r="B2" t="n">
-        <v>88728</v>
+        <v>88729</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59742-2024 artfynd.xlsx
+++ b/artfynd/A 59742-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127013878</v>
       </c>
       <c r="B2" t="n">
-        <v>88729</v>
+        <v>88733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127013854</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>127013855</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59742-2024 artfynd.xlsx
+++ b/artfynd/A 59742-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127013878</v>
       </c>
       <c r="B2" t="n">
-        <v>88733</v>
+        <v>88735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127013854</v>
       </c>
       <c r="B3" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>127013855</v>
       </c>
       <c r="B4" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59742-2024 artfynd.xlsx
+++ b/artfynd/A 59742-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>127013854</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>127013855</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59742-2024 artfynd.xlsx
+++ b/artfynd/A 59742-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>127013854</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>127013855</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59742-2024 artfynd.xlsx
+++ b/artfynd/A 59742-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127013878</v>
       </c>
       <c r="B2" t="n">
-        <v>88735</v>
+        <v>88722</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59742-2024 artfynd.xlsx
+++ b/artfynd/A 59742-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127013878</v>
       </c>
       <c r="B2" t="n">
-        <v>88735</v>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127013854</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>127013855</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,6 +973,108 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127013856</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Risede, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>507611</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7142461</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
